--- a/apps/cliente/public/examples/file_people.xlsx
+++ b/apps/cliente/public/examples/file_people.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="373">
   <si>
     <t>employee_code</t>
   </si>
@@ -25,6 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>termination_date</t>
+  </si>
+  <si>
+    <t>termination_reason_code</t>
+  </si>
+  <si>
     <t>email</t>
   </si>
   <si>
@@ -40,7 +46,19 @@
     <t>document_number</t>
   </si>
   <si>
-    <t>contract_type</t>
+    <t>manager_code</t>
+  </si>
+  <si>
+    <t>company_code</t>
+  </si>
+  <si>
+    <t>company_name</t>
+  </si>
+  <si>
+    <t>location_code</t>
+  </si>
+  <si>
+    <t>location_name</t>
   </si>
   <si>
     <t>area_code</t>
@@ -55,13 +73,10 @@
     <t>position_name</t>
   </si>
   <si>
-    <t>location_code</t>
-  </si>
-  <si>
-    <t>location_name</t>
-  </si>
-  <si>
-    <t>manager_code</t>
+    <t>contract_code</t>
+  </si>
+  <si>
+    <t>contract_name</t>
   </si>
   <si>
     <t>EMP001</t>
@@ -91,13 +106,22 @@
     <t>12345678</t>
   </si>
   <si>
-    <t>full_time</t>
-  </si>
-  <si>
-    <t>GER</t>
-  </si>
-  <si>
-    <t>Gerencia</t>
+    <t>ACME-SA</t>
+  </si>
+  <si>
+    <t>Acme S.A.</t>
+  </si>
+  <si>
+    <t>BUE</t>
+  </si>
+  <si>
+    <t>Buenos Aires</t>
+  </si>
+  <si>
+    <t>OPS</t>
+  </si>
+  <si>
+    <t>Operaciones</t>
   </si>
   <si>
     <t>GTE</t>
@@ -106,10 +130,10 @@
     <t>Gerente</t>
   </si>
   <si>
-    <t>BUE</t>
-  </si>
-  <si>
-    <t>Buenos Aires</t>
+    <t>indefinido</t>
+  </si>
+  <si>
+    <t>Indefinido</t>
   </si>
   <si>
     <t>EMP002</t>
@@ -142,7 +166,7 @@
     <t>DEV</t>
   </si>
   <si>
-    <t>Desarrollador</t>
+    <t>Desarrollador/a</t>
   </si>
   <si>
     <t>EMP003</t>
@@ -163,19 +187,949 @@
     <t>34567890</t>
   </si>
   <si>
-    <t>part_time</t>
-  </si>
-  <si>
     <t>RH</t>
   </si>
   <si>
     <t>Recursos Humanos</t>
   </si>
   <si>
-    <t>RRHH</t>
-  </si>
-  <si>
-    <t>Analista RRHH</t>
+    <t>ANA</t>
+  </si>
+  <si>
+    <t>Analista</t>
+  </si>
+  <si>
+    <t>EMP004</t>
+  </si>
+  <si>
+    <t>Daniela Acosta</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>daniela.acosta.4@empresa.com</t>
+  </si>
+  <si>
+    <t>1966-11-07</t>
+  </si>
+  <si>
+    <t>20004055</t>
+  </si>
+  <si>
+    <t>COR</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>FIN</t>
+  </si>
+  <si>
+    <t>Finanzas</t>
+  </si>
+  <si>
+    <t>SUP</t>
+  </si>
+  <si>
+    <t>Supervisor/a</t>
+  </si>
+  <si>
+    <t>EMP005</t>
+  </si>
+  <si>
+    <t>Romina López</t>
+  </si>
+  <si>
+    <t>2019-04-04</t>
+  </si>
+  <si>
+    <t>romina.lopez.5@empresa.com</t>
+  </si>
+  <si>
+    <t>1997-11-11</t>
+  </si>
+  <si>
+    <t>20005686</t>
+  </si>
+  <si>
+    <t>EJV</t>
+  </si>
+  <si>
+    <t>Ejecutivo/a de Cuentas</t>
+  </si>
+  <si>
+    <t>EMP006</t>
+  </si>
+  <si>
+    <t>Julieta Romero</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>julieta.romero.6@empresa.com</t>
+  </si>
+  <si>
+    <t>1993-01-13</t>
+  </si>
+  <si>
+    <t>20006248</t>
+  </si>
+  <si>
+    <t>ACME-SERV</t>
+  </si>
+  <si>
+    <t>Acme Servicios S.R.L.</t>
+  </si>
+  <si>
+    <t>VTA</t>
+  </si>
+  <si>
+    <t>Ventas</t>
+  </si>
+  <si>
+    <t>EMP007</t>
+  </si>
+  <si>
+    <t>Nicolás Romero</t>
+  </si>
+  <si>
+    <t>2022-05-02</t>
+  </si>
+  <si>
+    <t>nicolas.romero.7@empresa.com</t>
+  </si>
+  <si>
+    <t>1973-04-07</t>
+  </si>
+  <si>
+    <t>20007571</t>
+  </si>
+  <si>
+    <t>OPE</t>
+  </si>
+  <si>
+    <t>Operario/a</t>
+  </si>
+  <si>
+    <t>EMP008</t>
+  </si>
+  <si>
+    <t>Julieta Benítez</t>
+  </si>
+  <si>
+    <t>2022-05-18</t>
+  </si>
+  <si>
+    <t>julieta.benitez.8@empresa.com</t>
+  </si>
+  <si>
+    <t>1999-08-04</t>
+  </si>
+  <si>
+    <t>20008336</t>
+  </si>
+  <si>
+    <t>ROS</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>LOG</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>contractor</t>
+  </si>
+  <si>
+    <t>Contratista</t>
+  </si>
+  <si>
+    <t>EMP009</t>
+  </si>
+  <si>
+    <t>Federico Ramírez</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>federico.ramirez.9@empresa.com</t>
+  </si>
+  <si>
+    <t>1996-01-12</t>
+  </si>
+  <si>
+    <t>20009792</t>
+  </si>
+  <si>
+    <t>plazo_fijo</t>
+  </si>
+  <si>
+    <t>Plazo fijo</t>
+  </si>
+  <si>
+    <t>EMP010</t>
+  </si>
+  <si>
+    <t>Camila Pérez</t>
+  </si>
+  <si>
+    <t>2022-09-24</t>
+  </si>
+  <si>
+    <t>camila.perez.10@empresa.com</t>
+  </si>
+  <si>
+    <t>1972-01-19</t>
+  </si>
+  <si>
+    <t>20010553</t>
+  </si>
+  <si>
+    <t>EMP011</t>
+  </si>
+  <si>
+    <t>Julieta Álvarez</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>julieta.alvarez.11@empresa.com</t>
+  </si>
+  <si>
+    <t>1974-04-03</t>
+  </si>
+  <si>
+    <t>20011508</t>
+  </si>
+  <si>
+    <t>EMP012</t>
+  </si>
+  <si>
+    <t>Agustina García</t>
+  </si>
+  <si>
+    <t>2023-04-19</t>
+  </si>
+  <si>
+    <t>agustina.garcia.12@empresa.com</t>
+  </si>
+  <si>
+    <t>1966-06-05</t>
+  </si>
+  <si>
+    <t>20012673</t>
+  </si>
+  <si>
+    <t>EMP013</t>
+  </si>
+  <si>
+    <t>Gonzalo Ruiz</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>gonzalo.ruiz.13@empresa.com</t>
+  </si>
+  <si>
+    <t>1988-06-10</t>
+  </si>
+  <si>
+    <t>20013933</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>Administrativo/a</t>
+  </si>
+  <si>
+    <t>EMP014</t>
+  </si>
+  <si>
+    <t>Lucía Martínez</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>VOLUNTARY_RESIGNATION</t>
+  </si>
+  <si>
+    <t>lucia.martinez.14@empresa.com</t>
+  </si>
+  <si>
+    <t>1991-10-05</t>
+  </si>
+  <si>
+    <t>20014703</t>
+  </si>
+  <si>
+    <t>EMP015</t>
+  </si>
+  <si>
+    <t>Santiago García</t>
+  </si>
+  <si>
+    <t>2020-02-07</t>
+  </si>
+  <si>
+    <t>2025-01-10</t>
+  </si>
+  <si>
+    <t>santiago.garcia.15@empresa.com</t>
+  </si>
+  <si>
+    <t>1974-05-01</t>
+  </si>
+  <si>
+    <t>20015310</t>
+  </si>
+  <si>
+    <t>EMP016</t>
+  </si>
+  <si>
+    <t>Santiago Torres</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>DISMISSAL</t>
+  </si>
+  <si>
+    <t>santiago.torres.16@empresa.com</t>
+  </si>
+  <si>
+    <t>1997-11-04</t>
+  </si>
+  <si>
+    <t>20016615</t>
+  </si>
+  <si>
+    <t>EMP017</t>
+  </si>
+  <si>
+    <t>Nicolás Díaz</t>
+  </si>
+  <si>
+    <t>2024-10-01</t>
+  </si>
+  <si>
+    <t>nicolas.diaz.17@empresa.com</t>
+  </si>
+  <si>
+    <t>1974-09-28</t>
+  </si>
+  <si>
+    <t>20017460</t>
+  </si>
+  <si>
+    <t>EMP018</t>
+  </si>
+  <si>
+    <t>Carolina Herrera</t>
+  </si>
+  <si>
+    <t>2023-03-26</t>
+  </si>
+  <si>
+    <t>carolina.herrera.18@empresa.com</t>
+  </si>
+  <si>
+    <t>1980-11-14</t>
+  </si>
+  <si>
+    <t>20018569</t>
+  </si>
+  <si>
+    <t>EMP019</t>
+  </si>
+  <si>
+    <t>Florencia Acosta</t>
+  </si>
+  <si>
+    <t>2022-01-11</t>
+  </si>
+  <si>
+    <t>florencia.acosta.19@empresa.com</t>
+  </si>
+  <si>
+    <t>1987-04-02</t>
+  </si>
+  <si>
+    <t>20019714</t>
+  </si>
+  <si>
+    <t>EMP020</t>
+  </si>
+  <si>
+    <t>Gonzalo Suárez</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
+    <t>gonzalo.suarez.20@empresa.com</t>
+  </si>
+  <si>
+    <t>1995-02-13</t>
+  </si>
+  <si>
+    <t>20020492</t>
+  </si>
+  <si>
+    <t>EMP021</t>
+  </si>
+  <si>
+    <t>Ezequiel Díaz</t>
+  </si>
+  <si>
+    <t>2023-04-26</t>
+  </si>
+  <si>
+    <t>ezequiel.diaz.21@empresa.com</t>
+  </si>
+  <si>
+    <t>1967-02-22</t>
+  </si>
+  <si>
+    <t>20021529</t>
+  </si>
+  <si>
+    <t>EMP022</t>
+  </si>
+  <si>
+    <t>Ignacio Rodríguez</t>
+  </si>
+  <si>
+    <t>2025-10-26</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>ignacio.rodriguez.22@empresa.com</t>
+  </si>
+  <si>
+    <t>1972-08-28</t>
+  </si>
+  <si>
+    <t>20022860</t>
+  </si>
+  <si>
+    <t>EMP023</t>
+  </si>
+  <si>
+    <t>Florencia Álvarez</t>
+  </si>
+  <si>
+    <t>2025-11-07</t>
+  </si>
+  <si>
+    <t>florencia.alvarez.23@empresa.com</t>
+  </si>
+  <si>
+    <t>1975-10-15</t>
+  </si>
+  <si>
+    <t>20023951</t>
+  </si>
+  <si>
+    <t>EMP024</t>
+  </si>
+  <si>
+    <t>Federico Pérez</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>federico.perez.24@empresa.com</t>
+  </si>
+  <si>
+    <t>2002-02-21</t>
+  </si>
+  <si>
+    <t>20024608</t>
+  </si>
+  <si>
+    <t>EMP025</t>
+  </si>
+  <si>
+    <t>Camila González</t>
+  </si>
+  <si>
+    <t>2020-08-22</t>
+  </si>
+  <si>
+    <t>camila.gonzalez.25@empresa.com</t>
+  </si>
+  <si>
+    <t>1967-06-10</t>
+  </si>
+  <si>
+    <t>20026043</t>
+  </si>
+  <si>
+    <t>EMP026</t>
+  </si>
+  <si>
+    <t>Tomás Medina</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>tomas.medina.26@empresa.com</t>
+  </si>
+  <si>
+    <t>1981-11-09</t>
+  </si>
+  <si>
+    <t>20026456</t>
+  </si>
+  <si>
+    <t>EMP027</t>
+  </si>
+  <si>
+    <t>Daniela Rodríguez</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>daniela.rodriguez.27@empresa.com</t>
+  </si>
+  <si>
+    <t>1989-04-22</t>
+  </si>
+  <si>
+    <t>20027389</t>
+  </si>
+  <si>
+    <t>temporal</t>
+  </si>
+  <si>
+    <t>Temporal</t>
+  </si>
+  <si>
+    <t>EMP028</t>
+  </si>
+  <si>
+    <t>Agustina Acosta</t>
+  </si>
+  <si>
+    <t>2023-07-07</t>
+  </si>
+  <si>
+    <t>2025-02-11</t>
+  </si>
+  <si>
+    <t>BETTER_OFFER</t>
+  </si>
+  <si>
+    <t>agustina.acosta.28@empresa.com</t>
+  </si>
+  <si>
+    <t>1998-07-04</t>
+  </si>
+  <si>
+    <t>20028878</t>
+  </si>
+  <si>
+    <t>EMP029</t>
+  </si>
+  <si>
+    <t>Julieta González</t>
+  </si>
+  <si>
+    <t>2024-08-24</t>
+  </si>
+  <si>
+    <t>julieta.gonzalez.29@empresa.com</t>
+  </si>
+  <si>
+    <t>1976-11-07</t>
+  </si>
+  <si>
+    <t>20029775</t>
+  </si>
+  <si>
+    <t>EMP030</t>
+  </si>
+  <si>
+    <t>Valentina Sánchez</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>valentina.sanchez.30@empresa.com</t>
+  </si>
+  <si>
+    <t>1994-11-15</t>
+  </si>
+  <si>
+    <t>20030503</t>
+  </si>
+  <si>
+    <t>EMP031</t>
+  </si>
+  <si>
+    <t>Nicolás Ramírez</t>
+  </si>
+  <si>
+    <t>2020-02-08</t>
+  </si>
+  <si>
+    <t>nicolas.ramirez.31@empresa.com</t>
+  </si>
+  <si>
+    <t>2001-05-24</t>
+  </si>
+  <si>
+    <t>20031487</t>
+  </si>
+  <si>
+    <t>EMP032</t>
+  </si>
+  <si>
+    <t>Ignacio Benítez</t>
+  </si>
+  <si>
+    <t>2024-01-11</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>MUTUAL_AGREEMENT</t>
+  </si>
+  <si>
+    <t>ignacio.benitez.32@empresa.com</t>
+  </si>
+  <si>
+    <t>1985-12-13</t>
+  </si>
+  <si>
+    <t>20032728</t>
+  </si>
+  <si>
+    <t>EMP033</t>
+  </si>
+  <si>
+    <t>Paula Acosta</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>paula.acosta.33@empresa.com</t>
+  </si>
+  <si>
+    <t>1974-05-28</t>
+  </si>
+  <si>
+    <t>20034176</t>
+  </si>
+  <si>
+    <t>EMP034</t>
+  </si>
+  <si>
+    <t>Joaquín Pérez</t>
+  </si>
+  <si>
+    <t>2025-12-28</t>
+  </si>
+  <si>
+    <t>joaquin.perez.34@empresa.com</t>
+  </si>
+  <si>
+    <t>1972-03-15</t>
+  </si>
+  <si>
+    <t>20035339</t>
+  </si>
+  <si>
+    <t>EMP035</t>
+  </si>
+  <si>
+    <t>Carolina Martínez</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>carolina.martinez.35@empresa.com</t>
+  </si>
+  <si>
+    <t>1968-03-08</t>
+  </si>
+  <si>
+    <t>20035724</t>
+  </si>
+  <si>
+    <t>EMP036</t>
+  </si>
+  <si>
+    <t>Gonzalo Acosta</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>gonzalo.acosta.36@empresa.com</t>
+  </si>
+  <si>
+    <t>1994-06-15</t>
+  </si>
+  <si>
+    <t>20036776</t>
+  </si>
+  <si>
+    <t>EMP037</t>
+  </si>
+  <si>
+    <t>Julieta Fernández</t>
+  </si>
+  <si>
+    <t>2023-12-01</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>julieta.fernandez.37@empresa.com</t>
+  </si>
+  <si>
+    <t>1982-03-08</t>
+  </si>
+  <si>
+    <t>20037728</t>
+  </si>
+  <si>
+    <t>EMP038</t>
+  </si>
+  <si>
+    <t>Paula García</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>paula.garcia.38@empresa.com</t>
+  </si>
+  <si>
+    <t>1972-03-20</t>
+  </si>
+  <si>
+    <t>20039089</t>
+  </si>
+  <si>
+    <t>EMP039</t>
+  </si>
+  <si>
+    <t>Santiago López</t>
+  </si>
+  <si>
+    <t>2020-01-28</t>
+  </si>
+  <si>
+    <t>santiago.lopez.39@empresa.com</t>
+  </si>
+  <si>
+    <t>2000-08-15</t>
+  </si>
+  <si>
+    <t>20040319</t>
+  </si>
+  <si>
+    <t>EMP040</t>
+  </si>
+  <si>
+    <t>Julieta Ramírez</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>julieta.ramirez.40@empresa.com</t>
+  </si>
+  <si>
+    <t>1999-10-14</t>
+  </si>
+  <si>
+    <t>20040709</t>
+  </si>
+  <si>
+    <t>EMP041</t>
+  </si>
+  <si>
+    <t>Daniela Ramírez</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>daniela.ramirez.41@empresa.com</t>
+  </si>
+  <si>
+    <t>1994-05-04</t>
+  </si>
+  <si>
+    <t>20042393</t>
+  </si>
+  <si>
+    <t>EMP042</t>
+  </si>
+  <si>
+    <t>Lautaro Martínez</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>lautaro.martinez.42@empresa.com</t>
+  </si>
+  <si>
+    <t>1988-10-22</t>
+  </si>
+  <si>
+    <t>20043047</t>
+  </si>
+  <si>
+    <t>EMP043</t>
+  </si>
+  <si>
+    <t>2023-09-14</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>DISMISSAL_WITH_CAUSE</t>
+  </si>
+  <si>
+    <t>gonzalo.suarez.43@empresa.com</t>
+  </si>
+  <si>
+    <t>1995-04-26</t>
+  </si>
+  <si>
+    <t>20044388</t>
+  </si>
+  <si>
+    <t>EMP044</t>
+  </si>
+  <si>
+    <t>Nicolás Álvarez</t>
+  </si>
+  <si>
+    <t>2022-11-28</t>
+  </si>
+  <si>
+    <t>nicolas.alvarez.44@empresa.com</t>
+  </si>
+  <si>
+    <t>1981-12-09</t>
+  </si>
+  <si>
+    <t>20045301</t>
+  </si>
+  <si>
+    <t>EMP045</t>
+  </si>
+  <si>
+    <t>Agustina Rodríguez</t>
+  </si>
+  <si>
+    <t>2023-05-27</t>
+  </si>
+  <si>
+    <t>agustina.rodriguez.45@empresa.com</t>
+  </si>
+  <si>
+    <t>2001-10-18</t>
+  </si>
+  <si>
+    <t>20046403</t>
+  </si>
+  <si>
+    <t>EMP046</t>
+  </si>
+  <si>
+    <t>Nicolás García</t>
+  </si>
+  <si>
+    <t>2024-06-21</t>
+  </si>
+  <si>
+    <t>nicolas.garcia.46@empresa.com</t>
+  </si>
+  <si>
+    <t>1969-12-18</t>
+  </si>
+  <si>
+    <t>20046614</t>
+  </si>
+  <si>
+    <t>EMP047</t>
+  </si>
+  <si>
+    <t>Ignacio Ruiz</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>ignacio.ruiz.47@empresa.com</t>
+  </si>
+  <si>
+    <t>1992-11-16</t>
+  </si>
+  <si>
+    <t>20048506</t>
+  </si>
+  <si>
+    <t>EMP048</t>
+  </si>
+  <si>
+    <t>Lautaro Herrera</t>
+  </si>
+  <si>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>lautaro.herrera.48@empresa.com</t>
+  </si>
+  <si>
+    <t>1975-06-16</t>
+  </si>
+  <si>
+    <t>20048892</t>
   </si>
 </sst>
 </file>
@@ -194,17 +1148,12 @@
       <b/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -221,7 +1170,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,24 +1510,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="2" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="14" width="14" customWidth="1"/>
+    <col min="15" max="16" width="15" customWidth="1"/>
+    <col min="17" max="18" width="12" customWidth="1"/>
+    <col min="19" max="22" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,161 +1578,3053 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
         <v>31</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="O4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
+      <c r="P4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
+      <c r="Q4" t="s">
+        <v>58</v>
+      </c>
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" t="s">
+        <v>60</v>
+      </c>
+      <c r="T4" t="s">
+        <v>61</v>
+      </c>
+      <c r="U4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" t="s">
+        <v>71</v>
+      </c>
+      <c r="S5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s">
+        <v>73</v>
+      </c>
+      <c r="U5" t="s">
+        <v>39</v>
+      </c>
+      <c r="V5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" t="s">
+        <v>80</v>
+      </c>
+      <c r="T6" t="s">
+        <v>81</v>
+      </c>
+      <c r="U6" t="s">
+        <v>39</v>
+      </c>
+      <c r="V6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" t="s">
+        <v>89</v>
+      </c>
+      <c r="O7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>90</v>
+      </c>
+      <c r="R7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S7" t="s">
+        <v>37</v>
+      </c>
+      <c r="T7" t="s">
+        <v>38</v>
+      </c>
+      <c r="U7" t="s">
+        <v>39</v>
+      </c>
+      <c r="V7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" t="s">
         <v>35</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="R8" t="s">
         <v>36</v>
       </c>
-      <c r="F3" t="s">
+      <c r="S8" t="s">
+        <v>98</v>
+      </c>
+      <c r="T8" t="s">
+        <v>99</v>
+      </c>
+      <c r="U8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" t="s">
+        <v>106</v>
+      </c>
+      <c r="P9" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>108</v>
+      </c>
+      <c r="R9" t="s">
+        <v>109</v>
+      </c>
+      <c r="S9" t="s">
+        <v>50</v>
+      </c>
+      <c r="T9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U9" t="s">
+        <v>110</v>
+      </c>
+      <c r="V9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>90</v>
+      </c>
+      <c r="R10" t="s">
+        <v>91</v>
+      </c>
+      <c r="S10" t="s">
+        <v>98</v>
+      </c>
+      <c r="T10" t="s">
+        <v>99</v>
+      </c>
+      <c r="U10" t="s">
+        <v>118</v>
+      </c>
+      <c r="V10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" t="s">
+        <v>68</v>
+      </c>
+      <c r="P11" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" t="s">
+        <v>98</v>
+      </c>
+      <c r="T11" t="s">
+        <v>99</v>
+      </c>
+      <c r="U11" t="s">
+        <v>110</v>
+      </c>
+      <c r="V11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>70</v>
+      </c>
+      <c r="R12" t="s">
+        <v>71</v>
+      </c>
+      <c r="S12" t="s">
+        <v>60</v>
+      </c>
+      <c r="T12" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12" t="s">
+        <v>39</v>
+      </c>
+      <c r="V12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" t="s">
+        <v>137</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" t="s">
+        <v>33</v>
+      </c>
+      <c r="P13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>90</v>
+      </c>
+      <c r="R13" t="s">
+        <v>91</v>
+      </c>
+      <c r="S13" t="s">
+        <v>98</v>
+      </c>
+      <c r="T13" t="s">
+        <v>99</v>
+      </c>
+      <c r="U13" t="s">
+        <v>39</v>
+      </c>
+      <c r="V13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>88</v>
+      </c>
+      <c r="N14" t="s">
+        <v>89</v>
+      </c>
+      <c r="O14" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S14" t="s">
+        <v>144</v>
+      </c>
+      <c r="T14" t="s">
+        <v>145</v>
+      </c>
+      <c r="U14" t="s">
+        <v>39</v>
+      </c>
+      <c r="V14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" t="s">
+        <v>153</v>
+      </c>
+      <c r="I15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" t="s">
+        <v>154</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" t="s">
+        <v>68</v>
+      </c>
+      <c r="P15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S15" t="s">
         <v>37</v>
       </c>
-      <c r="G3" t="s">
+      <c r="T15" t="s">
         <v>38</v>
       </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="U15" t="s">
         <v>39</v>
       </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="V15" t="s">
         <v>40</v>
       </c>
-      <c r="L3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" t="s">
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" t="s">
+        <v>161</v>
+      </c>
+      <c r="L16" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s">
         <v>31</v>
       </c>
-      <c r="P3" t="s">
+      <c r="N16" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="O16" t="s">
+        <v>33</v>
+      </c>
+      <c r="P16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>90</v>
+      </c>
+      <c r="R16" t="s">
+        <v>91</v>
+      </c>
+      <c r="S16" t="s">
+        <v>98</v>
+      </c>
+      <c r="T16" t="s">
+        <v>99</v>
+      </c>
+      <c r="U16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F17" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" t="s">
+        <v>168</v>
+      </c>
+      <c r="I17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" t="s">
+        <v>169</v>
+      </c>
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" t="s">
+        <v>33</v>
+      </c>
+      <c r="P17" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>48</v>
+      </c>
+      <c r="R17" t="s">
+        <v>49</v>
+      </c>
+      <c r="S17" t="s">
+        <v>50</v>
+      </c>
+      <c r="T17" t="s">
+        <v>51</v>
+      </c>
+      <c r="U17" t="s">
+        <v>39</v>
+      </c>
+      <c r="V17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" t="s">
+        <v>174</v>
+      </c>
+      <c r="I18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" t="s">
+        <v>175</v>
+      </c>
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" t="s">
+        <v>72</v>
+      </c>
+      <c r="T18" t="s">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s">
+        <v>39</v>
+      </c>
+      <c r="V18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" t="s">
+        <v>180</v>
+      </c>
+      <c r="I19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" t="s">
+        <v>181</v>
+      </c>
+      <c r="L19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>70</v>
+      </c>
+      <c r="R19" t="s">
+        <v>71</v>
+      </c>
+      <c r="S19" t="s">
+        <v>98</v>
+      </c>
+      <c r="T19" t="s">
+        <v>99</v>
+      </c>
+      <c r="U19" t="s">
+        <v>39</v>
+      </c>
+      <c r="V19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" t="s">
+        <v>186</v>
+      </c>
+      <c r="I20" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="J20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" t="s">
+        <v>187</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" t="s">
+        <v>33</v>
+      </c>
+      <c r="P20" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>70</v>
+      </c>
+      <c r="R20" t="s">
+        <v>71</v>
+      </c>
+      <c r="S20" t="s">
+        <v>144</v>
+      </c>
+      <c r="T20" t="s">
+        <v>145</v>
+      </c>
+      <c r="U20" t="s">
+        <v>39</v>
+      </c>
+      <c r="V20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H21" t="s">
+        <v>192</v>
+      </c>
+      <c r="I21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" t="s">
+        <v>193</v>
+      </c>
+      <c r="L21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" t="s">
+        <v>89</v>
+      </c>
+      <c r="O21" t="s">
+        <v>33</v>
+      </c>
+      <c r="P21" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>90</v>
+      </c>
+      <c r="R21" t="s">
+        <v>91</v>
+      </c>
+      <c r="S21" t="s">
+        <v>98</v>
+      </c>
+      <c r="T21" t="s">
+        <v>99</v>
+      </c>
+      <c r="U21" t="s">
+        <v>39</v>
+      </c>
+      <c r="V21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22" t="s">
+        <v>198</v>
+      </c>
+      <c r="I22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" t="s">
+        <v>199</v>
+      </c>
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" t="s">
+        <v>88</v>
+      </c>
+      <c r="N22" t="s">
+        <v>89</v>
+      </c>
+      <c r="O22" t="s">
+        <v>68</v>
+      </c>
+      <c r="P22" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q22" t="s">
         <v>48</v>
       </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="R22" t="s">
         <v>49</v>
       </c>
-      <c r="J4" t="s">
+      <c r="S22" t="s">
+        <v>37</v>
+      </c>
+      <c r="T22" t="s">
+        <v>38</v>
+      </c>
+      <c r="U22" t="s">
+        <v>110</v>
+      </c>
+      <c r="V22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" t="s">
+        <v>203</v>
+      </c>
+      <c r="F23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G23" t="s">
+        <v>204</v>
+      </c>
+      <c r="H23" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s">
+        <v>206</v>
+      </c>
+      <c r="L23" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" t="s">
+        <v>88</v>
+      </c>
+      <c r="N23" t="s">
+        <v>89</v>
+      </c>
+      <c r="O23" t="s">
+        <v>33</v>
+      </c>
+      <c r="P23" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>36</v>
+      </c>
+      <c r="S23" t="s">
+        <v>60</v>
+      </c>
+      <c r="T23" t="s">
+        <v>61</v>
+      </c>
+      <c r="U23" t="s">
+        <v>39</v>
+      </c>
+      <c r="V23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" t="s">
+        <v>209</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>210</v>
+      </c>
+      <c r="H24" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" t="s">
+        <v>212</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>31</v>
+      </c>
+      <c r="N24" t="s">
+        <v>32</v>
+      </c>
+      <c r="O24" t="s">
+        <v>33</v>
+      </c>
+      <c r="P24" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>90</v>
+      </c>
+      <c r="R24" t="s">
+        <v>91</v>
+      </c>
+      <c r="S24" t="s">
         <v>50</v>
       </c>
-      <c r="K4" t="s">
+      <c r="T24" t="s">
         <v>51</v>
       </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N4" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="U24" t="s">
+        <v>39</v>
+      </c>
+      <c r="V24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>216</v>
+      </c>
+      <c r="H25" t="s">
+        <v>217</v>
+      </c>
+      <c r="I25" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" t="s">
+        <v>218</v>
+      </c>
+      <c r="L25" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s">
         <v>31</v>
       </c>
-      <c r="P4" t="s">
+      <c r="N25" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" t="s">
-        <v>17</v>
+      <c r="O25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P25" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" t="s">
+        <v>36</v>
+      </c>
+      <c r="S25" t="s">
+        <v>50</v>
+      </c>
+      <c r="T25" t="s">
+        <v>51</v>
+      </c>
+      <c r="U25" t="s">
+        <v>118</v>
+      </c>
+      <c r="V25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" t="s">
+        <v>221</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>222</v>
+      </c>
+      <c r="H26" t="s">
+        <v>223</v>
+      </c>
+      <c r="I26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" t="s">
+        <v>224</v>
+      </c>
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" t="s">
+        <v>31</v>
+      </c>
+      <c r="N26" t="s">
+        <v>32</v>
+      </c>
+      <c r="O26" t="s">
+        <v>33</v>
+      </c>
+      <c r="P26" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>48</v>
+      </c>
+      <c r="R26" t="s">
+        <v>49</v>
+      </c>
+      <c r="S26" t="s">
+        <v>98</v>
+      </c>
+      <c r="T26" t="s">
+        <v>99</v>
+      </c>
+      <c r="U26" t="s">
+        <v>39</v>
+      </c>
+      <c r="V26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" t="s">
+        <v>228</v>
+      </c>
+      <c r="F27" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" t="s">
+        <v>229</v>
+      </c>
+      <c r="H27" t="s">
+        <v>230</v>
+      </c>
+      <c r="I27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s">
+        <v>231</v>
+      </c>
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N27" t="s">
+        <v>89</v>
+      </c>
+      <c r="O27" t="s">
+        <v>33</v>
+      </c>
+      <c r="P27" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>90</v>
+      </c>
+      <c r="R27" t="s">
+        <v>91</v>
+      </c>
+      <c r="S27" t="s">
+        <v>50</v>
+      </c>
+      <c r="T27" t="s">
+        <v>51</v>
+      </c>
+      <c r="U27" t="s">
+        <v>110</v>
+      </c>
+      <c r="V27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>232</v>
+      </c>
+      <c r="B28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H28" t="s">
+        <v>236</v>
+      </c>
+      <c r="I28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" t="s">
+        <v>237</v>
+      </c>
+      <c r="L28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" t="s">
+        <v>106</v>
+      </c>
+      <c r="P28" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>48</v>
+      </c>
+      <c r="R28" t="s">
+        <v>49</v>
+      </c>
+      <c r="S28" t="s">
+        <v>98</v>
+      </c>
+      <c r="T28" t="s">
+        <v>99</v>
+      </c>
+      <c r="U28" t="s">
+        <v>238</v>
+      </c>
+      <c r="V28" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C29" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" t="s">
+        <v>243</v>
+      </c>
+      <c r="F29" t="s">
+        <v>244</v>
+      </c>
+      <c r="G29" t="s">
+        <v>245</v>
+      </c>
+      <c r="H29" t="s">
+        <v>246</v>
+      </c>
+      <c r="I29" t="s">
+        <v>46</v>
+      </c>
+      <c r="J29" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" t="s">
+        <v>247</v>
+      </c>
+      <c r="L29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" t="s">
+        <v>31</v>
+      </c>
+      <c r="N29" t="s">
+        <v>32</v>
+      </c>
+      <c r="O29" t="s">
+        <v>33</v>
+      </c>
+      <c r="P29" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>90</v>
+      </c>
+      <c r="R29" t="s">
+        <v>91</v>
+      </c>
+      <c r="S29" t="s">
+        <v>80</v>
+      </c>
+      <c r="T29" t="s">
+        <v>81</v>
+      </c>
+      <c r="U29" t="s">
+        <v>110</v>
+      </c>
+      <c r="V29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B30" t="s">
+        <v>249</v>
+      </c>
+      <c r="C30" t="s">
+        <v>250</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" t="s">
+        <v>251</v>
+      </c>
+      <c r="H30" t="s">
+        <v>252</v>
+      </c>
+      <c r="I30" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" t="s">
+        <v>253</v>
+      </c>
+      <c r="L30" t="s">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s">
+        <v>88</v>
+      </c>
+      <c r="N30" t="s">
+        <v>89</v>
+      </c>
+      <c r="O30" t="s">
+        <v>68</v>
+      </c>
+      <c r="P30" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>70</v>
+      </c>
+      <c r="R30" t="s">
+        <v>71</v>
+      </c>
+      <c r="S30" t="s">
+        <v>144</v>
+      </c>
+      <c r="T30" t="s">
+        <v>145</v>
+      </c>
+      <c r="U30" t="s">
+        <v>39</v>
+      </c>
+      <c r="V30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B31" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" t="s">
+        <v>256</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>257</v>
+      </c>
+      <c r="H31" t="s">
+        <v>258</v>
+      </c>
+      <c r="I31" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" t="s">
+        <v>259</v>
+      </c>
+      <c r="L31" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" t="s">
+        <v>31</v>
+      </c>
+      <c r="N31" t="s">
+        <v>32</v>
+      </c>
+      <c r="O31" t="s">
+        <v>33</v>
+      </c>
+      <c r="P31" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>108</v>
+      </c>
+      <c r="R31" t="s">
+        <v>109</v>
+      </c>
+      <c r="S31" t="s">
+        <v>80</v>
+      </c>
+      <c r="T31" t="s">
+        <v>81</v>
+      </c>
+      <c r="U31" t="s">
+        <v>39</v>
+      </c>
+      <c r="V31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>260</v>
+      </c>
+      <c r="B32" t="s">
+        <v>261</v>
+      </c>
+      <c r="C32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>263</v>
+      </c>
+      <c r="H32" t="s">
+        <v>264</v>
+      </c>
+      <c r="I32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" t="s">
+        <v>265</v>
+      </c>
+      <c r="L32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" t="s">
+        <v>31</v>
+      </c>
+      <c r="N32" t="s">
+        <v>32</v>
+      </c>
+      <c r="O32" t="s">
+        <v>106</v>
+      </c>
+      <c r="P32" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>48</v>
+      </c>
+      <c r="R32" t="s">
+        <v>49</v>
+      </c>
+      <c r="S32" t="s">
+        <v>72</v>
+      </c>
+      <c r="T32" t="s">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s">
+        <v>118</v>
+      </c>
+      <c r="V32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>266</v>
+      </c>
+      <c r="B33" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" t="s">
+        <v>268</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>269</v>
+      </c>
+      <c r="F33" t="s">
+        <v>270</v>
+      </c>
+      <c r="G33" t="s">
+        <v>271</v>
+      </c>
+      <c r="H33" t="s">
+        <v>272</v>
+      </c>
+      <c r="I33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" t="s">
+        <v>273</v>
+      </c>
+      <c r="L33" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N33" t="s">
+        <v>89</v>
+      </c>
+      <c r="O33" t="s">
+        <v>106</v>
+      </c>
+      <c r="P33" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>90</v>
+      </c>
+      <c r="R33" t="s">
+        <v>91</v>
+      </c>
+      <c r="S33" t="s">
+        <v>60</v>
+      </c>
+      <c r="T33" t="s">
+        <v>61</v>
+      </c>
+      <c r="U33" t="s">
+        <v>39</v>
+      </c>
+      <c r="V33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>274</v>
+      </c>
+      <c r="B34" t="s">
+        <v>275</v>
+      </c>
+      <c r="C34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" t="s">
+        <v>277</v>
+      </c>
+      <c r="H34" t="s">
+        <v>278</v>
+      </c>
+      <c r="I34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" t="s">
+        <v>279</v>
+      </c>
+      <c r="L34" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" t="s">
+        <v>33</v>
+      </c>
+      <c r="P34" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s">
+        <v>36</v>
+      </c>
+      <c r="S34" t="s">
+        <v>60</v>
+      </c>
+      <c r="T34" t="s">
+        <v>61</v>
+      </c>
+      <c r="U34" t="s">
+        <v>39</v>
+      </c>
+      <c r="V34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" t="s">
+        <v>281</v>
+      </c>
+      <c r="C35" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>283</v>
+      </c>
+      <c r="H35" t="s">
+        <v>284</v>
+      </c>
+      <c r="I35" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" t="s">
+        <v>285</v>
+      </c>
+      <c r="L35" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" t="s">
+        <v>31</v>
+      </c>
+      <c r="N35" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" t="s">
+        <v>68</v>
+      </c>
+      <c r="P35" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>48</v>
+      </c>
+      <c r="R35" t="s">
+        <v>49</v>
+      </c>
+      <c r="S35" t="s">
+        <v>60</v>
+      </c>
+      <c r="T35" t="s">
+        <v>61</v>
+      </c>
+      <c r="U35" t="s">
+        <v>39</v>
+      </c>
+      <c r="V35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>286</v>
+      </c>
+      <c r="B36" t="s">
+        <v>287</v>
+      </c>
+      <c r="C36" t="s">
+        <v>288</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>289</v>
+      </c>
+      <c r="H36" t="s">
+        <v>290</v>
+      </c>
+      <c r="I36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" t="s">
+        <v>291</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" t="s">
+        <v>31</v>
+      </c>
+      <c r="N36" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" t="s">
+        <v>33</v>
+      </c>
+      <c r="P36" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" t="s">
+        <v>36</v>
+      </c>
+      <c r="S36" t="s">
+        <v>37</v>
+      </c>
+      <c r="T36" t="s">
+        <v>38</v>
+      </c>
+      <c r="U36" t="s">
+        <v>238</v>
+      </c>
+      <c r="V36" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>292</v>
+      </c>
+      <c r="B37" t="s">
+        <v>293</v>
+      </c>
+      <c r="C37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D37" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" t="s">
+        <v>295</v>
+      </c>
+      <c r="F37" t="s">
+        <v>244</v>
+      </c>
+      <c r="G37" t="s">
+        <v>296</v>
+      </c>
+      <c r="H37" t="s">
+        <v>297</v>
+      </c>
+      <c r="I37" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" t="s">
+        <v>298</v>
+      </c>
+      <c r="L37" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" t="s">
+        <v>31</v>
+      </c>
+      <c r="N37" t="s">
+        <v>32</v>
+      </c>
+      <c r="O37" t="s">
+        <v>33</v>
+      </c>
+      <c r="P37" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>35</v>
+      </c>
+      <c r="R37" t="s">
+        <v>36</v>
+      </c>
+      <c r="S37" t="s">
+        <v>80</v>
+      </c>
+      <c r="T37" t="s">
+        <v>81</v>
+      </c>
+      <c r="U37" t="s">
+        <v>39</v>
+      </c>
+      <c r="V37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>299</v>
+      </c>
+      <c r="B38" t="s">
+        <v>300</v>
+      </c>
+      <c r="C38" t="s">
+        <v>301</v>
+      </c>
+      <c r="D38" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" t="s">
+        <v>302</v>
+      </c>
+      <c r="F38" t="s">
+        <v>151</v>
+      </c>
+      <c r="G38" t="s">
+        <v>303</v>
+      </c>
+      <c r="H38" t="s">
+        <v>304</v>
+      </c>
+      <c r="I38" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" t="s">
+        <v>305</v>
+      </c>
+      <c r="L38" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" t="s">
+        <v>31</v>
+      </c>
+      <c r="N38" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>108</v>
+      </c>
+      <c r="R38" t="s">
+        <v>109</v>
+      </c>
+      <c r="S38" t="s">
+        <v>98</v>
+      </c>
+      <c r="T38" t="s">
+        <v>99</v>
+      </c>
+      <c r="U38" t="s">
+        <v>39</v>
+      </c>
+      <c r="V38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>306</v>
+      </c>
+      <c r="B39" t="s">
+        <v>307</v>
+      </c>
+      <c r="C39" t="s">
+        <v>308</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
+        <v>309</v>
+      </c>
+      <c r="H39" t="s">
+        <v>310</v>
+      </c>
+      <c r="I39" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" t="s">
+        <v>311</v>
+      </c>
+      <c r="L39" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" t="s">
+        <v>31</v>
+      </c>
+      <c r="N39" t="s">
+        <v>32</v>
+      </c>
+      <c r="O39" t="s">
+        <v>33</v>
+      </c>
+      <c r="P39" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" t="s">
+        <v>36</v>
+      </c>
+      <c r="S39" t="s">
+        <v>60</v>
+      </c>
+      <c r="T39" t="s">
+        <v>61</v>
+      </c>
+      <c r="U39" t="s">
+        <v>39</v>
+      </c>
+      <c r="V39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>312</v>
+      </c>
+      <c r="B40" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" t="s">
+        <v>314</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" t="s">
+        <v>315</v>
+      </c>
+      <c r="H40" t="s">
+        <v>316</v>
+      </c>
+      <c r="I40" t="s">
+        <v>46</v>
+      </c>
+      <c r="J40" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" t="s">
+        <v>317</v>
+      </c>
+      <c r="L40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" t="s">
+        <v>31</v>
+      </c>
+      <c r="N40" t="s">
+        <v>32</v>
+      </c>
+      <c r="O40" t="s">
+        <v>33</v>
+      </c>
+      <c r="P40" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>90</v>
+      </c>
+      <c r="R40" t="s">
+        <v>91</v>
+      </c>
+      <c r="S40" t="s">
+        <v>50</v>
+      </c>
+      <c r="T40" t="s">
+        <v>51</v>
+      </c>
+      <c r="U40" t="s">
+        <v>39</v>
+      </c>
+      <c r="V40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>318</v>
+      </c>
+      <c r="B41" t="s">
+        <v>319</v>
+      </c>
+      <c r="C41" t="s">
+        <v>320</v>
+      </c>
+      <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" t="s">
+        <v>321</v>
+      </c>
+      <c r="H41" t="s">
+        <v>322</v>
+      </c>
+      <c r="I41" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" t="s">
+        <v>323</v>
+      </c>
+      <c r="L41" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" t="s">
+        <v>88</v>
+      </c>
+      <c r="N41" t="s">
+        <v>89</v>
+      </c>
+      <c r="O41" t="s">
+        <v>68</v>
+      </c>
+      <c r="P41" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>35</v>
+      </c>
+      <c r="R41" t="s">
+        <v>36</v>
+      </c>
+      <c r="S41" t="s">
+        <v>72</v>
+      </c>
+      <c r="T41" t="s">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s">
+        <v>39</v>
+      </c>
+      <c r="V41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>324</v>
+      </c>
+      <c r="B42" t="s">
+        <v>325</v>
+      </c>
+      <c r="C42" t="s">
+        <v>326</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" t="s">
+        <v>327</v>
+      </c>
+      <c r="H42" t="s">
+        <v>328</v>
+      </c>
+      <c r="I42" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" t="s">
+        <v>329</v>
+      </c>
+      <c r="L42" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" t="s">
+        <v>31</v>
+      </c>
+      <c r="N42" t="s">
+        <v>32</v>
+      </c>
+      <c r="O42" t="s">
+        <v>33</v>
+      </c>
+      <c r="P42" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>48</v>
+      </c>
+      <c r="R42" t="s">
+        <v>49</v>
+      </c>
+      <c r="S42" t="s">
+        <v>50</v>
+      </c>
+      <c r="T42" t="s">
+        <v>51</v>
+      </c>
+      <c r="U42" t="s">
+        <v>39</v>
+      </c>
+      <c r="V42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>330</v>
+      </c>
+      <c r="B43" t="s">
+        <v>331</v>
+      </c>
+      <c r="C43" t="s">
+        <v>332</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" t="s">
+        <v>333</v>
+      </c>
+      <c r="H43" t="s">
+        <v>334</v>
+      </c>
+      <c r="I43" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" t="s">
+        <v>335</v>
+      </c>
+      <c r="L43" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" t="s">
+        <v>32</v>
+      </c>
+      <c r="O43" t="s">
+        <v>33</v>
+      </c>
+      <c r="P43" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>48</v>
+      </c>
+      <c r="R43" t="s">
+        <v>49</v>
+      </c>
+      <c r="S43" t="s">
+        <v>60</v>
+      </c>
+      <c r="T43" t="s">
+        <v>61</v>
+      </c>
+      <c r="U43" t="s">
+        <v>39</v>
+      </c>
+      <c r="V43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>336</v>
+      </c>
+      <c r="B44" t="s">
+        <v>189</v>
+      </c>
+      <c r="C44" t="s">
+        <v>337</v>
+      </c>
+      <c r="D44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" t="s">
+        <v>338</v>
+      </c>
+      <c r="F44" t="s">
+        <v>339</v>
+      </c>
+      <c r="G44" t="s">
+        <v>340</v>
+      </c>
+      <c r="H44" t="s">
+        <v>341</v>
+      </c>
+      <c r="I44" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44" t="s">
+        <v>342</v>
+      </c>
+      <c r="L44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" t="s">
+        <v>32</v>
+      </c>
+      <c r="O44" t="s">
+        <v>106</v>
+      </c>
+      <c r="P44" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>90</v>
+      </c>
+      <c r="R44" t="s">
+        <v>91</v>
+      </c>
+      <c r="S44" t="s">
+        <v>144</v>
+      </c>
+      <c r="T44" t="s">
+        <v>145</v>
+      </c>
+      <c r="U44" t="s">
+        <v>39</v>
+      </c>
+      <c r="V44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>343</v>
+      </c>
+      <c r="B45" t="s">
+        <v>344</v>
+      </c>
+      <c r="C45" t="s">
+        <v>345</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" t="s">
+        <v>346</v>
+      </c>
+      <c r="H45" t="s">
+        <v>347</v>
+      </c>
+      <c r="I45" t="s">
+        <v>28</v>
+      </c>
+      <c r="J45" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" t="s">
+        <v>348</v>
+      </c>
+      <c r="L45" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" t="s">
+        <v>31</v>
+      </c>
+      <c r="N45" t="s">
+        <v>32</v>
+      </c>
+      <c r="O45" t="s">
+        <v>33</v>
+      </c>
+      <c r="P45" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>35</v>
+      </c>
+      <c r="R45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S45" t="s">
+        <v>80</v>
+      </c>
+      <c r="T45" t="s">
+        <v>81</v>
+      </c>
+      <c r="U45" t="s">
+        <v>39</v>
+      </c>
+      <c r="V45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>349</v>
+      </c>
+      <c r="B46" t="s">
+        <v>350</v>
+      </c>
+      <c r="C46" t="s">
+        <v>351</v>
+      </c>
+      <c r="D46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" t="s">
+        <v>352</v>
+      </c>
+      <c r="H46" t="s">
+        <v>353</v>
+      </c>
+      <c r="I46" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" t="s">
+        <v>354</v>
+      </c>
+      <c r="L46" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" t="s">
+        <v>88</v>
+      </c>
+      <c r="N46" t="s">
+        <v>89</v>
+      </c>
+      <c r="O46" t="s">
+        <v>106</v>
+      </c>
+      <c r="P46" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S46" t="s">
+        <v>80</v>
+      </c>
+      <c r="T46" t="s">
+        <v>81</v>
+      </c>
+      <c r="U46" t="s">
+        <v>39</v>
+      </c>
+      <c r="V46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>355</v>
+      </c>
+      <c r="B47" t="s">
+        <v>356</v>
+      </c>
+      <c r="C47" t="s">
+        <v>357</v>
+      </c>
+      <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>358</v>
+      </c>
+      <c r="H47" t="s">
+        <v>359</v>
+      </c>
+      <c r="I47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J47" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" t="s">
+        <v>360</v>
+      </c>
+      <c r="L47" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" t="s">
+        <v>88</v>
+      </c>
+      <c r="N47" t="s">
+        <v>89</v>
+      </c>
+      <c r="O47" t="s">
+        <v>33</v>
+      </c>
+      <c r="P47" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" t="s">
+        <v>36</v>
+      </c>
+      <c r="S47" t="s">
+        <v>144</v>
+      </c>
+      <c r="T47" t="s">
+        <v>145</v>
+      </c>
+      <c r="U47" t="s">
+        <v>39</v>
+      </c>
+      <c r="V47" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>361</v>
+      </c>
+      <c r="B48" t="s">
+        <v>362</v>
+      </c>
+      <c r="C48" t="s">
+        <v>363</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" t="s">
+        <v>364</v>
+      </c>
+      <c r="H48" t="s">
+        <v>365</v>
+      </c>
+      <c r="I48" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" t="s">
+        <v>366</v>
+      </c>
+      <c r="L48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" t="s">
+        <v>88</v>
+      </c>
+      <c r="N48" t="s">
+        <v>89</v>
+      </c>
+      <c r="O48" t="s">
+        <v>33</v>
+      </c>
+      <c r="P48" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>90</v>
+      </c>
+      <c r="R48" t="s">
+        <v>91</v>
+      </c>
+      <c r="S48" t="s">
+        <v>50</v>
+      </c>
+      <c r="T48" t="s">
+        <v>51</v>
+      </c>
+      <c r="U48" t="s">
+        <v>39</v>
+      </c>
+      <c r="V48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>367</v>
+      </c>
+      <c r="B49" t="s">
+        <v>368</v>
+      </c>
+      <c r="C49" t="s">
+        <v>369</v>
+      </c>
+      <c r="D49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" t="s">
+        <v>370</v>
+      </c>
+      <c r="H49" t="s">
+        <v>371</v>
+      </c>
+      <c r="I49" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" t="s">
+        <v>29</v>
+      </c>
+      <c r="K49" t="s">
+        <v>372</v>
+      </c>
+      <c r="L49" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" t="s">
+        <v>31</v>
+      </c>
+      <c r="N49" t="s">
+        <v>32</v>
+      </c>
+      <c r="O49" t="s">
+        <v>68</v>
+      </c>
+      <c r="P49" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" t="s">
+        <v>36</v>
+      </c>
+      <c r="S49" t="s">
+        <v>98</v>
+      </c>
+      <c r="T49" t="s">
+        <v>99</v>
+      </c>
+      <c r="U49" t="s">
+        <v>238</v>
+      </c>
+      <c r="V49" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
